--- a/Data/Gabarito_Resultados.xlsx
+++ b/Data/Gabarito_Resultados.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
-  <si>
-    <t>url</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+  <si>
+    <t>name</t>
   </si>
   <si>
     <t>manipulative_design_Gabarito</t>
@@ -239,37 +239,13 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Calibri,sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
-      </rPr>
-      <t>www.cartoonnetwork.ca</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Calibri,sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
-      </rPr>
-      <t>www.disney.com.br</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Calibri,sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
-      </rPr>
-      <t>www.nickelodeon.com.br</t>
-    </r>
+    <t>www.cartoonnetwork.ca/</t>
+  </si>
+  <si>
+    <t>www.disney.com.br/</t>
+  </si>
+  <si>
+    <t>www.nickelodeon.com.br/</t>
   </si>
   <si>
     <r>
@@ -294,15 +270,7 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Calibri,sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
-      </rPr>
-      <t>www.coquinhos.com</t>
-    </r>
+    <t>www.coquinhos.com/</t>
   </si>
   <si>
     <r>
@@ -327,22 +295,17 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Calibri,sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
-      </rPr>
-      <t>https://www.shein.com/</t>
-    </r>
+    <t>https://www.shein.com.br/</t>
+  </si>
+  <si>
+    <t>https://www.shopee.com.br/</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -361,8 +324,15 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <u/>
       <sz val="11.0"/>
-      <color rgb="FF000000"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11.0"/>
+      <color rgb="FF0000FF"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -380,7 +350,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -393,7 +363,12 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -612,7 +587,7 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="44.13"/>
-    <col customWidth="1" min="2" max="2" width="25.13"/>
+    <col customWidth="1" min="2" max="2" width="27.75"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -784,7 +759,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="4" t="s">
         <v>22</v>
       </c>
       <c r="B22" s="3" t="b">
@@ -792,7 +767,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="4" t="s">
         <v>23</v>
       </c>
       <c r="B23" s="3" t="b">
@@ -800,7 +775,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="4" t="s">
         <v>24</v>
       </c>
       <c r="B24" s="3" t="b">
@@ -824,7 +799,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="4" t="s">
         <v>27</v>
       </c>
       <c r="B27" s="3" t="b">
@@ -848,7 +823,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="4" t="s">
         <v>30</v>
       </c>
       <c r="B30" s="3" t="b">
@@ -856,7 +831,12 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4"/>
+      <c r="A31" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B31" s="3" t="b">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -889,7 +869,8 @@
     <hyperlink r:id="rId27" ref="A28"/>
     <hyperlink r:id="rId28" ref="A29"/>
     <hyperlink r:id="rId29" ref="A30"/>
+    <hyperlink r:id="rId30" ref="A31"/>
   </hyperlinks>
-  <drawing r:id="rId30"/>
+  <drawing r:id="rId31"/>
 </worksheet>
 </file>